--- a/questions_points.xlsx
+++ b/questions_points.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://purl.oclc.org/ooxml/spreadsheetml/main" xmlns:r="http://purl.oclc.org/ooxml/officeDocument/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2" conformance="strict">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10125"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10315"/>
   <workbookPr dateCompatibility="0" defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/kruppajo/work/GitHub/exam/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/jokruppa/GitHub/exam/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:9_{AEADD61A-11E5-F845-A213-65497244DC47}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:9_{B5356B3D-2EE6-FD43-8D51-438909E4F986}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="1040" windowWidth="21780" windowHeight="11900" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://purl.oclc.org/ooxml/spreadsheetml/main" count="77" uniqueCount="77">
+<sst xmlns="http://purl.oclc.org/ooxml/spreadsheetml/main" count="75" uniqueCount="75">
   <si>
     <t>file_name</t>
   </si>
@@ -249,12 +249,6 @@
   </si>
   <si>
     <t>forsch-lern-02.Rnw</t>
-  </si>
-  <si>
-    <t>program-R-01.Rnw</t>
-  </si>
-  <si>
-    <t>program-R-02.Rnw</t>
   </si>
   <si>
     <t>experiment-02.Rnw</t>
@@ -1136,7 +1130,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://purl.oclc.org/ooxml/spreadsheetml/main" xmlns:r="http://purl.oclc.org/ooxml/officeDocument/relationships" xmlns:v="urn:schemas-microsoft-com:vml" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:B76"/>
+  <dimension ref="A1:B74"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="38" bestFit="1" customWidth="1"/>
@@ -1216,7 +1210,7 @@
     </row>
     <row r="10" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A10" t="s">
-        <v>74</v>
+        <v>72</v>
       </c>
       <c r="B10">
         <v>10</v>
@@ -1232,7 +1226,7 @@
     </row>
     <row r="12" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A12" t="s">
-        <v>73</v>
+        <v>71</v>
       </c>
       <c r="B12">
         <v>20</v>
@@ -1400,7 +1394,7 @@
     </row>
     <row r="33" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A33" t="s">
-        <v>76</v>
+        <v>74</v>
       </c>
       <c r="B33">
         <v>10</v>
@@ -1536,23 +1530,23 @@
     </row>
     <row r="50" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A50" t="s">
-        <v>71</v>
+        <v>2</v>
       </c>
       <c r="B50">
-        <v>9</v>
+        <v>10</v>
       </c>
     </row>
     <row r="51" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A51" t="s">
-        <v>72</v>
+        <v>23</v>
       </c>
       <c r="B51">
-        <v>9</v>
+        <v>10</v>
       </c>
     </row>
     <row r="52" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A52" t="s">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="B52">
         <v>10</v>
@@ -1560,7 +1554,7 @@
     </row>
     <row r="53" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A53" t="s">
-        <v>23</v>
+        <v>4</v>
       </c>
       <c r="B53">
         <v>10</v>
@@ -1568,7 +1562,7 @@
     </row>
     <row r="54" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A54" t="s">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="B54">
         <v>10</v>
@@ -1576,7 +1570,7 @@
     </row>
     <row r="55" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A55" t="s">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="B55">
         <v>10</v>
@@ -1584,7 +1578,7 @@
     </row>
     <row r="56" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A56" t="s">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="B56">
         <v>10</v>
@@ -1592,7 +1586,7 @@
     </row>
     <row r="57" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A57" t="s">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="B57">
         <v>10</v>
@@ -1600,7 +1594,7 @@
     </row>
     <row r="58" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A58" t="s">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="B58">
         <v>10</v>
@@ -1608,7 +1602,7 @@
     </row>
     <row r="59" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A59" t="s">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="B59">
         <v>10</v>
@@ -1616,7 +1610,7 @@
     </row>
     <row r="60" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A60" t="s">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="B60">
         <v>10</v>
@@ -1624,7 +1618,7 @@
     </row>
     <row r="61" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A61" t="s">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="B61">
         <v>10</v>
@@ -1632,7 +1626,7 @@
     </row>
     <row r="62" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A62" t="s">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="B62">
         <v>10</v>
@@ -1640,7 +1634,7 @@
     </row>
     <row r="63" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A63" t="s">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="B63">
         <v>10</v>
@@ -1648,15 +1642,15 @@
     </row>
     <row r="64" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A64" t="s">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="B64">
-        <v>10</v>
+        <v>12</v>
       </c>
     </row>
     <row r="65" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A65" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="B65">
         <v>10</v>
@@ -1664,39 +1658,39 @@
     </row>
     <row r="66" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A66" t="s">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="B66">
-        <v>12</v>
+        <v>10</v>
       </c>
     </row>
     <row r="67" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A67" t="s">
-        <v>16</v>
+        <v>21</v>
       </c>
       <c r="B67">
-        <v>10</v>
+        <v>12</v>
       </c>
     </row>
     <row r="68" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A68" t="s">
-        <v>17</v>
+        <v>22</v>
       </c>
       <c r="B68">
-        <v>10</v>
+        <v>12</v>
       </c>
     </row>
     <row r="69" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A69" t="s">
-        <v>21</v>
+        <v>66</v>
       </c>
       <c r="B69">
-        <v>12</v>
+        <v>10</v>
       </c>
     </row>
     <row r="70" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A70" t="s">
-        <v>22</v>
+        <v>68</v>
       </c>
       <c r="B70">
         <v>12</v>
@@ -1704,23 +1698,23 @@
     </row>
     <row r="71" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A71" t="s">
-        <v>66</v>
+        <v>18</v>
       </c>
       <c r="B71">
-        <v>10</v>
+        <v>6</v>
       </c>
     </row>
     <row r="72" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A72" t="s">
-        <v>68</v>
+        <v>19</v>
       </c>
       <c r="B72">
-        <v>12</v>
+        <v>8</v>
       </c>
     </row>
     <row r="73" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A73" t="s">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="B73">
         <v>6</v>
@@ -1728,30 +1722,14 @@
     </row>
     <row r="74" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A74" t="s">
-        <v>19</v>
+        <v>73</v>
       </c>
       <c r="B74">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="75" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A75" t="s">
-        <v>20</v>
-      </c>
-      <c r="B75">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="76" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A76" t="s">
-        <v>75</v>
-      </c>
-      <c r="B76">
         <v>10</v>
       </c>
     </row>
   </sheetData>
-  <conditionalFormatting sqref="B2:B76">
+  <conditionalFormatting sqref="B2:B74">
     <cfRule type="cellIs" dxfId="1" priority="1" operator="lessThan">
       <formula>9</formula>
     </cfRule>

--- a/questions_points.xlsx
+++ b/questions_points.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://purl.oclc.org/ooxml/spreadsheetml/main" xmlns:r="http://purl.oclc.org/ooxml/officeDocument/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2" conformance="strict">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10315"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10503"/>
   <workbookPr dateCompatibility="0" defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/jokruppa/GitHub/exam/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:9_{B5356B3D-2EE6-FD43-8D51-438909E4F986}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:9_{1555F32B-343B-6645-81F6-267234FC641D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="1040" windowWidth="21780" windowHeight="11900" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -1357,7 +1357,7 @@
         <v>38</v>
       </c>
       <c r="B28">
-        <v>10</v>
+        <v>11</v>
       </c>
     </row>
     <row r="29" spans="1:2" x14ac:dyDescent="0.2">

--- a/questions_points.xlsx
+++ b/questions_points.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://purl.oclc.org/ooxml/spreadsheetml/main" xmlns:r="http://purl.oclc.org/ooxml/officeDocument/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2" conformance="strict">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10503"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10525"/>
   <workbookPr dateCompatibility="0" defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/jokruppa/GitHub/exam/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:9_{1555F32B-343B-6645-81F6-267234FC641D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:9_{E9D0EE15-63B0-2F42-B0DF-44C7DAEB9B22}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="1040" windowWidth="21780" windowHeight="11900" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -1725,7 +1725,7 @@
         <v>73</v>
       </c>
       <c r="B74">
-        <v>10</v>
+        <v>12</v>
       </c>
     </row>
   </sheetData>

--- a/questions_points.xlsx
+++ b/questions_points.xlsx
@@ -5,12 +5,12 @@
   <workbookPr dateCompatibility="0" defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/jokruppa/GitHub/exam/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/kruppajo/work/GitHub/exam/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:9_{E9D0EE15-63B0-2F42-B0DF-44C7DAEB9B22}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:9_{4E0E8BAC-F3A7-9046-8E66-F3B0CA7134B2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="1040" windowWidth="21780" windowHeight="11900" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="44700" yWindow="13480" windowWidth="23200" windowHeight="14660" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="questions_points" sheetId="1" r:id="rId1"/>
@@ -1149,7 +1149,7 @@
         <v>57</v>
       </c>
       <c r="B2">
-        <v>9</v>
+        <v>11</v>
       </c>
     </row>
     <row r="3" spans="1:2" x14ac:dyDescent="0.2">
@@ -1157,7 +1157,7 @@
         <v>58</v>
       </c>
       <c r="B3">
-        <v>8</v>
+        <v>10</v>
       </c>
     </row>
     <row r="4" spans="1:2" x14ac:dyDescent="0.2">
@@ -1165,7 +1165,7 @@
         <v>59</v>
       </c>
       <c r="B4">
-        <v>9</v>
+        <v>11</v>
       </c>
     </row>
     <row r="5" spans="1:2" x14ac:dyDescent="0.2">
@@ -1173,7 +1173,7 @@
         <v>60</v>
       </c>
       <c r="B5">
-        <v>9</v>
+        <v>12</v>
       </c>
     </row>
     <row r="6" spans="1:2" x14ac:dyDescent="0.2">

--- a/questions_points.xlsx
+++ b/questions_points.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/kruppajo/work/GitHub/exam/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:9_{4E0E8BAC-F3A7-9046-8E66-F3B0CA7134B2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:9_{4D7371D6-5C68-C14F-A9D8-3F58497DDB4B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="44700" yWindow="13480" windowWidth="23200" windowHeight="14660" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -1181,7 +1181,7 @@
         <v>61</v>
       </c>
       <c r="B6">
-        <v>10</v>
+        <v>12</v>
       </c>
     </row>
     <row r="7" spans="1:2" x14ac:dyDescent="0.2">

--- a/questions_points.xlsx
+++ b/questions_points.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/kruppajo/work/GitHub/exam/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:9_{4D7371D6-5C68-C14F-A9D8-3F58497DDB4B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:9_{086CE0EF-31B6-2049-8FF1-94D2607B80C0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="44700" yWindow="13480" windowWidth="23200" windowHeight="14660" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="600" windowWidth="38400" windowHeight="19940" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="questions_points" sheetId="1" r:id="rId1"/>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://purl.oclc.org/ooxml/spreadsheetml/main" count="75" uniqueCount="75">
+<sst xmlns="http://purl.oclc.org/ooxml/spreadsheetml/main" count="72" uniqueCount="72">
   <si>
     <t>file_name</t>
   </si>
@@ -90,15 +90,6 @@
   </si>
   <si>
     <t>math-17.Rnw</t>
-  </si>
-  <si>
-    <t>tier-01.Rnw</t>
-  </si>
-  <si>
-    <t>tier-02.Rnw</t>
-  </si>
-  <si>
-    <t>tier-03.Rnw</t>
   </si>
   <si>
     <t>math-18.Rnw</t>
@@ -1130,7 +1121,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://purl.oclc.org/ooxml/spreadsheetml/main" xmlns:r="http://purl.oclc.org/ooxml/officeDocument/relationships" xmlns:v="urn:schemas-microsoft-com:vml" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:B74"/>
+  <dimension ref="A1:B71"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="38" bestFit="1" customWidth="1"/>
@@ -1146,7 +1137,7 @@
     </row>
     <row r="2" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A2" t="s">
-        <v>57</v>
+        <v>54</v>
       </c>
       <c r="B2">
         <v>11</v>
@@ -1154,7 +1145,7 @@
     </row>
     <row r="3" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A3" t="s">
-        <v>58</v>
+        <v>55</v>
       </c>
       <c r="B3">
         <v>10</v>
@@ -1162,7 +1153,7 @@
     </row>
     <row r="4" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A4" s="1" t="s">
-        <v>59</v>
+        <v>56</v>
       </c>
       <c r="B4">
         <v>11</v>
@@ -1170,7 +1161,7 @@
     </row>
     <row r="5" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A5" t="s">
-        <v>60</v>
+        <v>57</v>
       </c>
       <c r="B5">
         <v>12</v>
@@ -1178,15 +1169,15 @@
     </row>
     <row r="6" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A6" t="s">
-        <v>61</v>
+        <v>58</v>
       </c>
       <c r="B6">
-        <v>12</v>
+        <v>11</v>
       </c>
     </row>
     <row r="7" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A7" s="1" t="s">
-        <v>62</v>
+        <v>59</v>
       </c>
       <c r="B7">
         <v>10</v>
@@ -1194,7 +1185,7 @@
     </row>
     <row r="8" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A8" t="s">
-        <v>63</v>
+        <v>60</v>
       </c>
       <c r="B8">
         <v>8</v>
@@ -1202,7 +1193,7 @@
     </row>
     <row r="9" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A9" t="s">
-        <v>64</v>
+        <v>61</v>
       </c>
       <c r="B9">
         <v>8</v>
@@ -1210,7 +1201,7 @@
     </row>
     <row r="10" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A10" t="s">
-        <v>72</v>
+        <v>69</v>
       </c>
       <c r="B10">
         <v>10</v>
@@ -1218,7 +1209,7 @@
     </row>
     <row r="11" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A11" t="s">
-        <v>67</v>
+        <v>64</v>
       </c>
       <c r="B11">
         <v>16</v>
@@ -1226,7 +1217,7 @@
     </row>
     <row r="12" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A12" t="s">
-        <v>71</v>
+        <v>68</v>
       </c>
       <c r="B12">
         <v>20</v>
@@ -1234,31 +1225,31 @@
     </row>
     <row r="13" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A13" t="s">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="B13">
-        <v>9</v>
+        <v>11</v>
       </c>
     </row>
     <row r="14" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A14" t="s">
-        <v>25</v>
+        <v>22</v>
       </c>
       <c r="B14">
-        <v>9</v>
+        <v>10</v>
       </c>
     </row>
     <row r="15" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A15" t="s">
-        <v>26</v>
+        <v>23</v>
       </c>
       <c r="B15">
-        <v>9</v>
+        <v>12</v>
       </c>
     </row>
     <row r="16" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A16" t="s">
-        <v>27</v>
+        <v>24</v>
       </c>
       <c r="B16">
         <v>10</v>
@@ -1266,7 +1257,7 @@
     </row>
     <row r="17" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A17" t="s">
-        <v>28</v>
+        <v>25</v>
       </c>
       <c r="B17">
         <v>10</v>
@@ -1274,15 +1265,15 @@
     </row>
     <row r="18" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A18" t="s">
-        <v>29</v>
+        <v>26</v>
       </c>
       <c r="B18">
-        <v>9</v>
+        <v>11</v>
       </c>
     </row>
     <row r="19" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A19" t="s">
-        <v>30</v>
+        <v>27</v>
       </c>
       <c r="B19">
         <v>12</v>
@@ -1290,7 +1281,7 @@
     </row>
     <row r="20" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A20" t="s">
-        <v>31</v>
+        <v>28</v>
       </c>
       <c r="B20">
         <v>12</v>
@@ -1298,7 +1289,7 @@
     </row>
     <row r="21" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A21" t="s">
-        <v>32</v>
+        <v>29</v>
       </c>
       <c r="B21">
         <v>11</v>
@@ -1306,7 +1297,7 @@
     </row>
     <row r="22" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A22" t="s">
-        <v>33</v>
+        <v>30</v>
       </c>
       <c r="B22">
         <v>10</v>
@@ -1314,7 +1305,7 @@
     </row>
     <row r="23" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A23" t="s">
-        <v>34</v>
+        <v>31</v>
       </c>
       <c r="B23">
         <v>10</v>
@@ -1322,7 +1313,7 @@
     </row>
     <row r="24" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A24" t="s">
-        <v>35</v>
+        <v>32</v>
       </c>
       <c r="B24">
         <v>11</v>
@@ -1330,7 +1321,7 @@
     </row>
     <row r="25" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A25" t="s">
-        <v>65</v>
+        <v>62</v>
       </c>
       <c r="B25">
         <v>10</v>
@@ -1338,7 +1329,7 @@
     </row>
     <row r="26" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A26" t="s">
-        <v>36</v>
+        <v>33</v>
       </c>
       <c r="B26">
         <v>11</v>
@@ -1346,7 +1337,7 @@
     </row>
     <row r="27" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A27" t="s">
-        <v>37</v>
+        <v>34</v>
       </c>
       <c r="B27">
         <v>10</v>
@@ -1354,7 +1345,7 @@
     </row>
     <row r="28" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A28" t="s">
-        <v>38</v>
+        <v>35</v>
       </c>
       <c r="B28">
         <v>11</v>
@@ -1362,7 +1353,7 @@
     </row>
     <row r="29" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A29" t="s">
-        <v>39</v>
+        <v>36</v>
       </c>
       <c r="B29">
         <v>12</v>
@@ -1370,7 +1361,7 @@
     </row>
     <row r="30" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A30" t="s">
-        <v>40</v>
+        <v>37</v>
       </c>
       <c r="B30">
         <v>12</v>
@@ -1378,7 +1369,7 @@
     </row>
     <row r="31" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A31" t="s">
-        <v>41</v>
+        <v>38</v>
       </c>
       <c r="B31">
         <v>12</v>
@@ -1386,7 +1377,7 @@
     </row>
     <row r="32" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A32" t="s">
-        <v>42</v>
+        <v>39</v>
       </c>
       <c r="B32">
         <v>12</v>
@@ -1394,7 +1385,7 @@
     </row>
     <row r="33" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A33" t="s">
-        <v>74</v>
+        <v>71</v>
       </c>
       <c r="B33">
         <v>10</v>
@@ -1402,7 +1393,7 @@
     </row>
     <row r="34" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A34" t="s">
-        <v>43</v>
+        <v>40</v>
       </c>
       <c r="B34">
         <v>10</v>
@@ -1410,7 +1401,7 @@
     </row>
     <row r="35" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A35" t="s">
-        <v>44</v>
+        <v>41</v>
       </c>
       <c r="B35">
         <v>10</v>
@@ -1418,7 +1409,7 @@
     </row>
     <row r="36" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A36" t="s">
-        <v>45</v>
+        <v>42</v>
       </c>
       <c r="B36">
         <v>11</v>
@@ -1426,7 +1417,7 @@
     </row>
     <row r="37" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A37" t="s">
-        <v>46</v>
+        <v>43</v>
       </c>
       <c r="B37">
         <v>10</v>
@@ -1434,7 +1425,7 @@
     </row>
     <row r="38" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A38" t="s">
-        <v>50</v>
+        <v>47</v>
       </c>
       <c r="B38">
         <v>12</v>
@@ -1442,7 +1433,7 @@
     </row>
     <row r="39" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A39" t="s">
-        <v>51</v>
+        <v>48</v>
       </c>
       <c r="B39">
         <v>11</v>
@@ -1450,7 +1441,7 @@
     </row>
     <row r="40" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A40" t="s">
-        <v>52</v>
+        <v>49</v>
       </c>
       <c r="B40">
         <v>10</v>
@@ -1458,7 +1449,7 @@
     </row>
     <row r="41" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A41" t="s">
-        <v>53</v>
+        <v>50</v>
       </c>
       <c r="B41">
         <v>12</v>
@@ -1466,7 +1457,7 @@
     </row>
     <row r="42" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A42" t="s">
-        <v>54</v>
+        <v>51</v>
       </c>
       <c r="B42">
         <v>12</v>
@@ -1474,7 +1465,7 @@
     </row>
     <row r="43" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A43" t="s">
-        <v>55</v>
+        <v>52</v>
       </c>
       <c r="B43">
         <v>11</v>
@@ -1482,7 +1473,7 @@
     </row>
     <row r="44" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A44" t="s">
-        <v>56</v>
+        <v>53</v>
       </c>
       <c r="B44">
         <v>12</v>
@@ -1490,7 +1481,7 @@
     </row>
     <row r="45" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A45" t="s">
-        <v>47</v>
+        <v>44</v>
       </c>
       <c r="B45">
         <v>12</v>
@@ -1498,7 +1489,7 @@
     </row>
     <row r="46" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A46" t="s">
-        <v>49</v>
+        <v>46</v>
       </c>
       <c r="B46">
         <v>10</v>
@@ -1506,7 +1497,7 @@
     </row>
     <row r="47" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A47" t="s">
-        <v>48</v>
+        <v>45</v>
       </c>
       <c r="B47">
         <v>10</v>
@@ -1514,7 +1505,7 @@
     </row>
     <row r="48" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A48" t="s">
-        <v>69</v>
+        <v>66</v>
       </c>
       <c r="B48">
         <v>20</v>
@@ -1522,7 +1513,7 @@
     </row>
     <row r="49" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A49" t="s">
-        <v>70</v>
+        <v>67</v>
       </c>
       <c r="B49">
         <v>20</v>
@@ -1538,7 +1529,7 @@
     </row>
     <row r="51" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A51" t="s">
-        <v>23</v>
+        <v>20</v>
       </c>
       <c r="B51">
         <v>10</v>
@@ -1666,7 +1657,7 @@
     </row>
     <row r="67" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A67" t="s">
-        <v>21</v>
+        <v>18</v>
       </c>
       <c r="B67">
         <v>12</v>
@@ -1674,7 +1665,7 @@
     </row>
     <row r="68" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A68" t="s">
-        <v>22</v>
+        <v>19</v>
       </c>
       <c r="B68">
         <v>12</v>
@@ -1682,7 +1673,7 @@
     </row>
     <row r="69" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A69" t="s">
-        <v>66</v>
+        <v>63</v>
       </c>
       <c r="B69">
         <v>10</v>
@@ -1690,7 +1681,7 @@
     </row>
     <row r="70" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A70" t="s">
-        <v>68</v>
+        <v>65</v>
       </c>
       <c r="B70">
         <v>12</v>
@@ -1698,38 +1689,14 @@
     </row>
     <row r="71" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A71" t="s">
-        <v>18</v>
+        <v>70</v>
       </c>
       <c r="B71">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="72" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A72" t="s">
-        <v>19</v>
-      </c>
-      <c r="B72">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="73" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A73" t="s">
-        <v>20</v>
-      </c>
-      <c r="B73">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="74" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A74" t="s">
-        <v>73</v>
-      </c>
-      <c r="B74">
         <v>12</v>
       </c>
     </row>
   </sheetData>
-  <conditionalFormatting sqref="B2:B74">
+  <conditionalFormatting sqref="B2:B71">
     <cfRule type="cellIs" dxfId="1" priority="1" operator="lessThan">
       <formula>9</formula>
     </cfRule>

--- a/questions_points.xlsx
+++ b/questions_points.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://purl.oclc.org/ooxml/spreadsheetml/main" xmlns:r="http://purl.oclc.org/ooxml/officeDocument/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2" conformance="strict">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10525"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10621"/>
   <workbookPr dateCompatibility="0" defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/kruppajo/work/GitHub/exam/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/jokruppa/GitHub/exam/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:9_{086CE0EF-31B6-2049-8FF1-94D2607B80C0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:9_{5084B5CE-6DA9-844A-99D9-588E97B84C2F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="600" windowWidth="38400" windowHeight="19940" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://purl.oclc.org/ooxml/spreadsheetml/main" count="72" uniqueCount="72">
+<sst xmlns="http://purl.oclc.org/ooxml/spreadsheetml/main" count="71" uniqueCount="71">
   <si>
     <t>file_name</t>
   </si>
@@ -243,9 +243,6 @@
   </si>
   <si>
     <t>experiment-02.Rnw</t>
-  </si>
-  <si>
-    <t>desc_stat-09.Rnw</t>
   </si>
   <si>
     <t>hausarbeit-01.Rnw</t>
@@ -1121,13 +1118,13 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://purl.oclc.org/ooxml/spreadsheetml/main" xmlns:r="http://purl.oclc.org/ooxml/officeDocument/relationships" xmlns:v="urn:schemas-microsoft-com:vml" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:B71"/>
+  <dimension ref="A1:D70"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="38" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -1135,7 +1132,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="2" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A2" t="s">
         <v>54</v>
       </c>
@@ -1143,7 +1140,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="3" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A3" t="s">
         <v>55</v>
       </c>
@@ -1151,7 +1148,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="4" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A4" s="1" t="s">
         <v>56</v>
       </c>
@@ -1159,7 +1156,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="5" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A5" t="s">
         <v>57</v>
       </c>
@@ -1167,7 +1164,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="6" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A6" t="s">
         <v>58</v>
       </c>
@@ -1175,7 +1172,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="7" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A7" s="1" t="s">
         <v>59</v>
       </c>
@@ -1183,73 +1180,77 @@
         <v>10</v>
       </c>
     </row>
-    <row r="8" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A8" t="s">
         <v>60</v>
       </c>
       <c r="B8">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="9" spans="1:2" x14ac:dyDescent="0.2">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="9" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A9" t="s">
         <v>61</v>
       </c>
       <c r="B9">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="10" spans="1:2" x14ac:dyDescent="0.2">
+        <v>11</v>
+      </c>
+      <c r="D9">
+        <f>+D17</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="10" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A10" t="s">
-        <v>69</v>
+        <v>64</v>
       </c>
       <c r="B10">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="11" spans="1:2" x14ac:dyDescent="0.2">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="11" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A11" t="s">
-        <v>64</v>
+        <v>68</v>
       </c>
       <c r="B11">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="12" spans="1:2" x14ac:dyDescent="0.2">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="12" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A12" t="s">
-        <v>68</v>
+        <v>21</v>
       </c>
       <c r="B12">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="13" spans="1:2" x14ac:dyDescent="0.2">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="13" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A13" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="B13">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="14" spans="1:2" x14ac:dyDescent="0.2">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="14" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A14" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="B14">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="15" spans="1:2" x14ac:dyDescent="0.2">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="15" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A15" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="B15">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="16" spans="1:2" x14ac:dyDescent="0.2">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="16" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A16" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="B16">
         <v>10</v>
@@ -1257,23 +1258,23 @@
     </row>
     <row r="17" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A17" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="B17">
-        <v>10</v>
+        <v>11</v>
       </c>
     </row>
     <row r="18" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A18" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="B18">
-        <v>11</v>
+        <v>12</v>
       </c>
     </row>
     <row r="19" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A19" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="B19">
         <v>12</v>
@@ -1281,23 +1282,23 @@
     </row>
     <row r="20" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A20" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="B20">
-        <v>12</v>
+        <v>11</v>
       </c>
     </row>
     <row r="21" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A21" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="B21">
-        <v>11</v>
+        <v>10</v>
       </c>
     </row>
     <row r="22" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A22" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="B22">
         <v>10</v>
@@ -1305,55 +1306,55 @@
     </row>
     <row r="23" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A23" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="B23">
-        <v>10</v>
+        <v>11</v>
       </c>
     </row>
     <row r="24" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A24" t="s">
-        <v>32</v>
+        <v>62</v>
       </c>
       <c r="B24">
-        <v>11</v>
+        <v>10</v>
       </c>
     </row>
     <row r="25" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A25" t="s">
-        <v>62</v>
+        <v>33</v>
       </c>
       <c r="B25">
-        <v>10</v>
+        <v>11</v>
       </c>
     </row>
     <row r="26" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A26" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="B26">
-        <v>11</v>
+        <v>10</v>
       </c>
     </row>
     <row r="27" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A27" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="B27">
-        <v>10</v>
+        <v>11</v>
       </c>
     </row>
     <row r="28" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A28" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="B28">
-        <v>11</v>
+        <v>12</v>
       </c>
     </row>
     <row r="29" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A29" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="B29">
         <v>12</v>
@@ -1361,7 +1362,7 @@
     </row>
     <row r="30" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A30" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="B30">
         <v>12</v>
@@ -1369,7 +1370,7 @@
     </row>
     <row r="31" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A31" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="B31">
         <v>12</v>
@@ -1377,15 +1378,15 @@
     </row>
     <row r="32" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A32" t="s">
-        <v>39</v>
+        <v>70</v>
       </c>
       <c r="B32">
-        <v>12</v>
+        <v>10</v>
       </c>
     </row>
     <row r="33" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A33" t="s">
-        <v>71</v>
+        <v>40</v>
       </c>
       <c r="B33">
         <v>10</v>
@@ -1393,7 +1394,7 @@
     </row>
     <row r="34" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A34" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="B34">
         <v>10</v>
@@ -1401,55 +1402,55 @@
     </row>
     <row r="35" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A35" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="B35">
-        <v>10</v>
+        <v>11</v>
       </c>
     </row>
     <row r="36" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A36" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="B36">
-        <v>11</v>
+        <v>10</v>
       </c>
     </row>
     <row r="37" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A37" t="s">
-        <v>43</v>
+        <v>47</v>
       </c>
       <c r="B37">
-        <v>10</v>
+        <v>12</v>
       </c>
     </row>
     <row r="38" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A38" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="B38">
-        <v>12</v>
+        <v>11</v>
       </c>
     </row>
     <row r="39" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A39" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="B39">
-        <v>11</v>
+        <v>10</v>
       </c>
     </row>
     <row r="40" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A40" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="B40">
-        <v>10</v>
+        <v>12</v>
       </c>
     </row>
     <row r="41" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A41" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="B41">
         <v>12</v>
@@ -1457,23 +1458,23 @@
     </row>
     <row r="42" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A42" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="B42">
-        <v>12</v>
+        <v>11</v>
       </c>
     </row>
     <row r="43" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A43" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="B43">
-        <v>11</v>
+        <v>12</v>
       </c>
     </row>
     <row r="44" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A44" t="s">
-        <v>53</v>
+        <v>44</v>
       </c>
       <c r="B44">
         <v>12</v>
@@ -1481,15 +1482,15 @@
     </row>
     <row r="45" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A45" t="s">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="B45">
-        <v>12</v>
+        <v>10</v>
       </c>
     </row>
     <row r="46" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A46" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="B46">
         <v>10</v>
@@ -1497,15 +1498,15 @@
     </row>
     <row r="47" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A47" t="s">
-        <v>45</v>
+        <v>66</v>
       </c>
       <c r="B47">
-        <v>10</v>
+        <v>20</v>
       </c>
     </row>
     <row r="48" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A48" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="B48">
         <v>20</v>
@@ -1513,15 +1514,15 @@
     </row>
     <row r="49" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A49" t="s">
-        <v>67</v>
+        <v>2</v>
       </c>
       <c r="B49">
-        <v>20</v>
+        <v>10</v>
       </c>
     </row>
     <row r="50" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A50" t="s">
-        <v>2</v>
+        <v>20</v>
       </c>
       <c r="B50">
         <v>10</v>
@@ -1529,7 +1530,7 @@
     </row>
     <row r="51" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A51" t="s">
-        <v>20</v>
+        <v>3</v>
       </c>
       <c r="B51">
         <v>10</v>
@@ -1537,7 +1538,7 @@
     </row>
     <row r="52" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A52" t="s">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="B52">
         <v>10</v>
@@ -1545,7 +1546,7 @@
     </row>
     <row r="53" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A53" t="s">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="B53">
         <v>10</v>
@@ -1553,7 +1554,7 @@
     </row>
     <row r="54" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A54" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="B54">
         <v>10</v>
@@ -1561,7 +1562,7 @@
     </row>
     <row r="55" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A55" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="B55">
         <v>10</v>
@@ -1569,7 +1570,7 @@
     </row>
     <row r="56" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A56" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="B56">
         <v>10</v>
@@ -1577,7 +1578,7 @@
     </row>
     <row r="57" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A57" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="B57">
         <v>10</v>
@@ -1585,7 +1586,7 @@
     </row>
     <row r="58" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A58" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="B58">
         <v>10</v>
@@ -1593,7 +1594,7 @@
     </row>
     <row r="59" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A59" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="B59">
         <v>10</v>
@@ -1601,7 +1602,7 @@
     </row>
     <row r="60" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A60" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="B60">
         <v>10</v>
@@ -1609,7 +1610,7 @@
     </row>
     <row r="61" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A61" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="B61">
         <v>10</v>
@@ -1617,7 +1618,7 @@
     </row>
     <row r="62" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A62" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="B62">
         <v>10</v>
@@ -1625,23 +1626,23 @@
     </row>
     <row r="63" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A63" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="B63">
-        <v>10</v>
+        <v>12</v>
       </c>
     </row>
     <row r="64" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A64" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="B64">
-        <v>12</v>
+        <v>10</v>
       </c>
     </row>
     <row r="65" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A65" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="B65">
         <v>10</v>
@@ -1649,15 +1650,15 @@
     </row>
     <row r="66" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A66" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="B66">
-        <v>10</v>
+        <v>12</v>
       </c>
     </row>
     <row r="67" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A67" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="B67">
         <v>12</v>
@@ -1665,38 +1666,30 @@
     </row>
     <row r="68" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A68" t="s">
-        <v>19</v>
+        <v>63</v>
       </c>
       <c r="B68">
-        <v>12</v>
+        <v>10</v>
       </c>
     </row>
     <row r="69" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A69" t="s">
-        <v>63</v>
+        <v>65</v>
       </c>
       <c r="B69">
-        <v>10</v>
+        <v>12</v>
       </c>
     </row>
     <row r="70" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A70" t="s">
-        <v>65</v>
+        <v>69</v>
       </c>
       <c r="B70">
         <v>12</v>
       </c>
     </row>
-    <row r="71" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A71" t="s">
-        <v>70</v>
-      </c>
-      <c r="B71">
-        <v>12</v>
-      </c>
-    </row>
   </sheetData>
-  <conditionalFormatting sqref="B2:B71">
+  <conditionalFormatting sqref="B2:B70">
     <cfRule type="cellIs" dxfId="1" priority="1" operator="lessThan">
       <formula>9</formula>
     </cfRule>

--- a/questions_points.xlsx
+++ b/questions_points.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/jokruppa/GitHub/exam/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:9_{5084B5CE-6DA9-844A-99D9-588E97B84C2F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:9_{9F2DEF7F-7805-3548-A007-A38F58A3605F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="600" windowWidth="38400" windowHeight="19940" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://purl.oclc.org/ooxml/spreadsheetml/main" count="71" uniqueCount="71">
+<sst xmlns="http://purl.oclc.org/ooxml/spreadsheetml/main" count="70" uniqueCount="70">
   <si>
     <t>file_name</t>
   </si>
@@ -219,9 +219,6 @@
   </si>
   <si>
     <t>desc_stat-07.Rnw</t>
-  </si>
-  <si>
-    <t>desc_stat-08.Rnw</t>
   </si>
   <si>
     <t>ttest-08.Rnw</t>
@@ -1118,13 +1115,13 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://purl.oclc.org/ooxml/spreadsheetml/main" xmlns:r="http://purl.oclc.org/ooxml/officeDocument/relationships" xmlns:v="urn:schemas-microsoft-com:vml" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:D70"/>
+  <dimension ref="A1:B69"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="38" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -1132,7 +1129,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="2" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A2" t="s">
         <v>54</v>
       </c>
@@ -1140,7 +1137,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="3" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A3" t="s">
         <v>55</v>
       </c>
@@ -1148,7 +1145,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="4" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A4" s="1" t="s">
         <v>56</v>
       </c>
@@ -1156,7 +1153,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="5" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A5" t="s">
         <v>57</v>
       </c>
@@ -1164,7 +1161,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="6" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A6" t="s">
         <v>58</v>
       </c>
@@ -1172,7 +1169,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="7" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A7" s="1" t="s">
         <v>59</v>
       </c>
@@ -1180,7 +1177,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="8" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A8" t="s">
         <v>60</v>
       </c>
@@ -1188,85 +1185,81 @@
         <v>11</v>
       </c>
     </row>
-    <row r="9" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A9" t="s">
-        <v>61</v>
+        <v>63</v>
       </c>
       <c r="B9">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="10" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A10" t="s">
+        <v>67</v>
+      </c>
+      <c r="B10">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="11" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A11" t="s">
+        <v>21</v>
+      </c>
+      <c r="B11">
         <v>11</v>
       </c>
-      <c r="D9">
-        <f>+D17</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="10" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A10" t="s">
-        <v>64</v>
-      </c>
-      <c r="B10">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="11" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A11" t="s">
-        <v>68</v>
-      </c>
-      <c r="B11">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="12" spans="1:4" x14ac:dyDescent="0.2">
+    </row>
+    <row r="12" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A12" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="B12">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="13" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A13" t="s">
+        <v>23</v>
+      </c>
+      <c r="B13">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="14" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A14" t="s">
+        <v>24</v>
+      </c>
+      <c r="B14">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="15" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A15" t="s">
+        <v>25</v>
+      </c>
+      <c r="B15">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="16" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A16" t="s">
+        <v>26</v>
+      </c>
+      <c r="B16">
         <v>11</v>
-      </c>
-    </row>
-    <row r="13" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A13" t="s">
-        <v>22</v>
-      </c>
-      <c r="B13">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="14" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A14" t="s">
-        <v>23</v>
-      </c>
-      <c r="B14">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="15" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A15" t="s">
-        <v>24</v>
-      </c>
-      <c r="B15">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="16" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A16" t="s">
-        <v>25</v>
-      </c>
-      <c r="B16">
-        <v>10</v>
       </c>
     </row>
     <row r="17" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A17" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="B17">
-        <v>11</v>
+        <v>12</v>
       </c>
     </row>
     <row r="18" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A18" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="B18">
         <v>12</v>
@@ -1274,23 +1267,23 @@
     </row>
     <row r="19" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A19" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="B19">
-        <v>12</v>
+        <v>11</v>
       </c>
     </row>
     <row r="20" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A20" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="B20">
-        <v>11</v>
+        <v>10</v>
       </c>
     </row>
     <row r="21" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A21" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="B21">
         <v>10</v>
@@ -1298,55 +1291,55 @@
     </row>
     <row r="22" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A22" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="B22">
-        <v>10</v>
+        <v>11</v>
       </c>
     </row>
     <row r="23" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A23" t="s">
-        <v>32</v>
+        <v>61</v>
       </c>
       <c r="B23">
-        <v>11</v>
+        <v>10</v>
       </c>
     </row>
     <row r="24" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A24" t="s">
-        <v>62</v>
+        <v>33</v>
       </c>
       <c r="B24">
-        <v>10</v>
+        <v>11</v>
       </c>
     </row>
     <row r="25" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A25" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="B25">
-        <v>11</v>
+        <v>10</v>
       </c>
     </row>
     <row r="26" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A26" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="B26">
-        <v>10</v>
+        <v>11</v>
       </c>
     </row>
     <row r="27" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A27" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="B27">
-        <v>11</v>
+        <v>12</v>
       </c>
     </row>
     <row r="28" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A28" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="B28">
         <v>12</v>
@@ -1354,7 +1347,7 @@
     </row>
     <row r="29" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A29" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="B29">
         <v>12</v>
@@ -1362,7 +1355,7 @@
     </row>
     <row r="30" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A30" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="B30">
         <v>12</v>
@@ -1370,15 +1363,15 @@
     </row>
     <row r="31" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A31" t="s">
-        <v>39</v>
+        <v>69</v>
       </c>
       <c r="B31">
-        <v>12</v>
+        <v>10</v>
       </c>
     </row>
     <row r="32" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A32" t="s">
-        <v>70</v>
+        <v>40</v>
       </c>
       <c r="B32">
         <v>10</v>
@@ -1386,7 +1379,7 @@
     </row>
     <row r="33" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A33" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="B33">
         <v>10</v>
@@ -1394,55 +1387,55 @@
     </row>
     <row r="34" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A34" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="B34">
-        <v>10</v>
+        <v>11</v>
       </c>
     </row>
     <row r="35" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A35" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="B35">
-        <v>11</v>
+        <v>10</v>
       </c>
     </row>
     <row r="36" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A36" t="s">
-        <v>43</v>
+        <v>47</v>
       </c>
       <c r="B36">
-        <v>10</v>
+        <v>12</v>
       </c>
     </row>
     <row r="37" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A37" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="B37">
-        <v>12</v>
+        <v>11</v>
       </c>
     </row>
     <row r="38" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A38" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="B38">
-        <v>11</v>
+        <v>10</v>
       </c>
     </row>
     <row r="39" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A39" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="B39">
-        <v>10</v>
+        <v>12</v>
       </c>
     </row>
     <row r="40" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A40" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="B40">
         <v>12</v>
@@ -1450,23 +1443,23 @@
     </row>
     <row r="41" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A41" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="B41">
-        <v>12</v>
+        <v>11</v>
       </c>
     </row>
     <row r="42" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A42" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="B42">
-        <v>11</v>
+        <v>12</v>
       </c>
     </row>
     <row r="43" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A43" t="s">
-        <v>53</v>
+        <v>44</v>
       </c>
       <c r="B43">
         <v>12</v>
@@ -1474,15 +1467,15 @@
     </row>
     <row r="44" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A44" t="s">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="B44">
-        <v>12</v>
+        <v>10</v>
       </c>
     </row>
     <row r="45" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A45" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="B45">
         <v>10</v>
@@ -1490,10 +1483,10 @@
     </row>
     <row r="46" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A46" t="s">
-        <v>45</v>
+        <v>65</v>
       </c>
       <c r="B46">
-        <v>10</v>
+        <v>20</v>
       </c>
     </row>
     <row r="47" spans="1:2" x14ac:dyDescent="0.2">
@@ -1506,15 +1499,15 @@
     </row>
     <row r="48" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A48" t="s">
-        <v>67</v>
+        <v>2</v>
       </c>
       <c r="B48">
-        <v>20</v>
+        <v>10</v>
       </c>
     </row>
     <row r="49" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A49" t="s">
-        <v>2</v>
+        <v>20</v>
       </c>
       <c r="B49">
         <v>10</v>
@@ -1522,7 +1515,7 @@
     </row>
     <row r="50" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A50" t="s">
-        <v>20</v>
+        <v>3</v>
       </c>
       <c r="B50">
         <v>10</v>
@@ -1530,7 +1523,7 @@
     </row>
     <row r="51" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A51" t="s">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="B51">
         <v>10</v>
@@ -1538,7 +1531,7 @@
     </row>
     <row r="52" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A52" t="s">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="B52">
         <v>10</v>
@@ -1546,7 +1539,7 @@
     </row>
     <row r="53" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A53" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="B53">
         <v>10</v>
@@ -1554,7 +1547,7 @@
     </row>
     <row r="54" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A54" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="B54">
         <v>10</v>
@@ -1562,7 +1555,7 @@
     </row>
     <row r="55" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A55" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="B55">
         <v>10</v>
@@ -1570,7 +1563,7 @@
     </row>
     <row r="56" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A56" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="B56">
         <v>10</v>
@@ -1578,7 +1571,7 @@
     </row>
     <row r="57" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A57" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="B57">
         <v>10</v>
@@ -1586,7 +1579,7 @@
     </row>
     <row r="58" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A58" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="B58">
         <v>10</v>
@@ -1594,7 +1587,7 @@
     </row>
     <row r="59" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A59" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="B59">
         <v>10</v>
@@ -1602,7 +1595,7 @@
     </row>
     <row r="60" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A60" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="B60">
         <v>10</v>
@@ -1610,7 +1603,7 @@
     </row>
     <row r="61" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A61" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="B61">
         <v>10</v>
@@ -1618,23 +1611,23 @@
     </row>
     <row r="62" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A62" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="B62">
-        <v>10</v>
+        <v>12</v>
       </c>
     </row>
     <row r="63" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A63" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="B63">
-        <v>12</v>
+        <v>10</v>
       </c>
     </row>
     <row r="64" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A64" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="B64">
         <v>10</v>
@@ -1642,15 +1635,15 @@
     </row>
     <row r="65" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A65" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="B65">
-        <v>10</v>
+        <v>12</v>
       </c>
     </row>
     <row r="66" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A66" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="B66">
         <v>12</v>
@@ -1658,38 +1651,30 @@
     </row>
     <row r="67" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A67" t="s">
-        <v>19</v>
+        <v>62</v>
       </c>
       <c r="B67">
-        <v>12</v>
+        <v>10</v>
       </c>
     </row>
     <row r="68" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A68" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="B68">
-        <v>10</v>
+        <v>12</v>
       </c>
     </row>
     <row r="69" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A69" t="s">
-        <v>65</v>
+        <v>68</v>
       </c>
       <c r="B69">
         <v>12</v>
       </c>
     </row>
-    <row r="70" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A70" t="s">
-        <v>69</v>
-      </c>
-      <c r="B70">
-        <v>12</v>
-      </c>
-    </row>
   </sheetData>
-  <conditionalFormatting sqref="B2:B70">
+  <conditionalFormatting sqref="B2:B69">
     <cfRule type="cellIs" dxfId="1" priority="1" operator="lessThan">
       <formula>9</formula>
     </cfRule>

--- a/questions_points.xlsx
+++ b/questions_points.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://purl.oclc.org/ooxml/spreadsheetml/main" xmlns:r="http://purl.oclc.org/ooxml/officeDocument/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2" conformance="strict">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10621"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10628"/>
   <workbookPr dateCompatibility="0" defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/jokruppa/GitHub/exam/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:9_{9F2DEF7F-7805-3548-A007-A38F58A3605F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:9_{5CAD4609-0E20-5A41-8AD9-57528E60F299}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="600" windowWidth="38400" windowHeight="19940" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -1358,7 +1358,7 @@
         <v>39</v>
       </c>
       <c r="B30">
-        <v>12</v>
+        <v>11</v>
       </c>
     </row>
     <row r="31" spans="1:2" x14ac:dyDescent="0.2">

--- a/questions_points.xlsx
+++ b/questions_points.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://purl.oclc.org/ooxml/spreadsheetml/main" xmlns:r="http://purl.oclc.org/ooxml/officeDocument/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2" conformance="strict">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10628"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10703"/>
   <workbookPr dateCompatibility="0" defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/jokruppa/GitHub/exam/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:9_{5CAD4609-0E20-5A41-8AD9-57528E60F299}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:9_{316DA52D-2DAC-9C46-AB3E-E23C310143D8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="600" windowWidth="38400" windowHeight="19940" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="23420" yWindow="2960" windowWidth="14980" windowHeight="17580" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="questions_points" sheetId="1" r:id="rId1"/>
@@ -1270,7 +1270,7 @@
         <v>29</v>
       </c>
       <c r="B19">
-        <v>11</v>
+        <v>10</v>
       </c>
     </row>
     <row r="20" spans="1:2" x14ac:dyDescent="0.2">

--- a/questions_points.xlsx
+++ b/questions_points.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://purl.oclc.org/ooxml/spreadsheetml/main" xmlns:r="http://purl.oclc.org/ooxml/officeDocument/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2" conformance="strict">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10703"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10802"/>
   <workbookPr dateCompatibility="0" defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/jokruppa/GitHub/exam/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:9_{316DA52D-2DAC-9C46-AB3E-E23C310143D8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:9_{AC99D2F6-E76A-4448-9D86-15B137492BE8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="23420" yWindow="2960" windowWidth="14980" windowHeight="17580" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -1502,7 +1502,7 @@
         <v>2</v>
       </c>
       <c r="B48">
-        <v>10</v>
+        <v>12</v>
       </c>
     </row>
     <row r="49" spans="1:2" x14ac:dyDescent="0.2">
@@ -1518,7 +1518,7 @@
         <v>3</v>
       </c>
       <c r="B50">
-        <v>10</v>
+        <v>12</v>
       </c>
     </row>
     <row r="51" spans="1:2" x14ac:dyDescent="0.2">

--- a/questions_points.xlsx
+++ b/questions_points.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://purl.oclc.org/ooxml/spreadsheetml/main" xmlns:r="http://purl.oclc.org/ooxml/officeDocument/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2" conformance="strict">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10802"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10821"/>
   <workbookPr dateCompatibility="0" defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/jokruppa/GitHub/exam/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:9_{AC99D2F6-E76A-4448-9D86-15B137492BE8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:9_{CC9A86A9-54AE-8446-8D60-1ED029BD83A6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="23420" yWindow="2960" windowWidth="14980" windowHeight="17580" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -1574,7 +1574,7 @@
         <v>10</v>
       </c>
       <c r="B57">
-        <v>10</v>
+        <v>12</v>
       </c>
     </row>
     <row r="58" spans="1:2" x14ac:dyDescent="0.2">

--- a/questions_points.xlsx
+++ b/questions_points.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/jokruppa/GitHub/exam/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:9_{CC9A86A9-54AE-8446-8D60-1ED029BD83A6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:9_{A54B105E-8CE8-AA4A-BFE9-030ADAC7A720}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="23420" yWindow="2960" windowWidth="14980" windowHeight="17580" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -1510,7 +1510,7 @@
         <v>20</v>
       </c>
       <c r="B49">
-        <v>10</v>
+        <v>12</v>
       </c>
     </row>
     <row r="50" spans="1:2" x14ac:dyDescent="0.2">
